--- a/resources/HEARTH_Production_Timeline.xlsx
+++ b/resources/HEARTH_Production_Timeline.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="213">
   <si>
     <t xml:space="preserve">HEARTH  ·  Indie Film Production Timeline</t>
   </si>
@@ -576,6 +576,9 @@
   </si>
   <si>
     <t xml:space="preserve">⚠ = Critical milestone — do not proceed to next phase without completing this task   |   Red rows = gates that block production</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Short Film 8-Week Quick Plan</t>
@@ -666,7 +669,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -762,6 +765,14 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF8B1A0A"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -931,11 +942,15 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1032,7 +1047,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1040,11 +1059,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1300,1295 +1319,1307 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B1:H67"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="2" t="s">
+      <c r="C4" s="4"/>
+      <c r="D4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="4"/>
+      <c r="F4" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="4"/>
+      <c r="H4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="8" t="s">
+      <c r="E8" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="8" t="s">
+      <c r="G8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="9" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="8" t="s">
+      <c r="G9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="9" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="8" t="s">
+      <c r="E10" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="9" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="8" t="s">
+      <c r="E11" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="G11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="8" t="s">
+      <c r="E12" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="8" t="s">
+      <c r="G12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="8" t="s">
+      <c r="E13" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="8" t="s">
+      <c r="G13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="9" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="8" t="s">
+      <c r="E14" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="8" t="s">
+      <c r="G14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="9" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="9" t="s">
+      <c r="D15" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="E15" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="11" t="s">
+      <c r="G15" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="12" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="12" t="s">
+      <c r="B17" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
+      <c r="B18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="14" t="s">
+      <c r="E18" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="14" t="s">
+      <c r="G18" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="15" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
+      <c r="B19" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="14" t="s">
+      <c r="E19" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="14" t="s">
+      <c r="G19" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="15" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
+      <c r="B20" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="14" t="s">
+      <c r="E20" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="14" t="s">
+      <c r="G20" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="15" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
+      <c r="B21" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="14" t="s">
+      <c r="E21" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="14" t="s">
+      <c r="G21" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="15" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
+      <c r="B22" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="14" t="s">
+      <c r="E22" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="14" t="s">
+      <c r="G22" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="15" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
+      <c r="B23" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="C23" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="13" t="s">
+      <c r="D23" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="14" t="s">
+      <c r="E23" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="14" t="s">
+      <c r="G23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="15" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
+      <c r="B24" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="14" t="s">
+      <c r="C24" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="14" t="s">
+      <c r="E24" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="14" t="s">
+      <c r="G24" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="15" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
+      <c r="B25" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="14" t="s">
+      <c r="E25" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="14" t="s">
+      <c r="G25" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="15" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
+      <c r="B26" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="14" t="s">
+      <c r="E26" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="14" t="s">
+      <c r="G26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="15" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="D27" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="11" t="s">
+      <c r="E27" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="G27" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="11" t="s">
+      <c r="G27" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
+      <c r="B28" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="C28" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="14" t="s">
+      <c r="E28" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="14" t="s">
+      <c r="G28" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="15" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="14" t="s">
+      <c r="E29" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="15" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="14" t="s">
+      <c r="G29" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="15" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="15" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="14" t="s">
+      <c r="E30" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" s="14" t="s">
+      <c r="G30" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="15" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="14" t="s">
+      <c r="E31" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="14" t="s">
+      <c r="G31" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="14" t="s">
+      <c r="E32" s="14" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G32" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="14" t="s">
+      <c r="G32" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="15" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="15" t="s">
+      <c r="B34" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="17" t="s">
+      <c r="C35" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="16" t="s">
+      <c r="D35" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="17" t="s">
+      <c r="E35" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="17" t="s">
+      <c r="G35" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="18" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E36" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="17" t="s">
+      <c r="E36" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="17" t="s">
+      <c r="G36" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="18" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="17" t="s">
+      <c r="C37" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E37" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="17" t="s">
+      <c r="E37" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="17" t="s">
+      <c r="G37" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="18" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="16" t="s">
+      <c r="D38" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E38" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="17" t="s">
+      <c r="E38" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G38" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="17" t="s">
+      <c r="G38" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="18" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="9" t="s">
+      <c r="B39" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="10" t="s">
+      <c r="C39" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="11" t="s">
+      <c r="E39" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="G39" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" s="11" t="s">
+      <c r="G39" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="12" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="16" t="s">
+      <c r="D40" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E40" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" s="17" t="s">
+      <c r="E40" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G40" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H40" s="17" t="s">
+      <c r="G40" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="18" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="17" t="s">
+      <c r="C41" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="16" t="s">
+      <c r="D41" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="E41" s="16" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="17" t="s">
+      <c r="E41" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="G41" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="17" t="s">
+      <c r="G41" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="18" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18"/>
-      <c r="G43" s="18"/>
-      <c r="H43" s="18"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
+      <c r="F43" s="19"/>
+      <c r="G43" s="19"/>
+      <c r="H43" s="19"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="19" t="s">
+      <c r="B44" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="20" t="s">
+      <c r="C44" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="19" t="s">
+      <c r="D44" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F44" s="20" t="s">
+      <c r="E44" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="G44" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="20" t="s">
+      <c r="G44" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="21" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="19" t="s">
+      <c r="B45" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="20" t="s">
+      <c r="C45" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="19" t="s">
+      <c r="D45" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" s="20" t="s">
+      <c r="E45" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="20" t="s">
+      <c r="G45" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="21" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="19" t="s">
+      <c r="B46" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="D46" s="19" t="s">
+      <c r="D46" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E46" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F46" s="20" t="s">
+      <c r="E46" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="20" t="s">
+      <c r="G46" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="21" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="9" t="s">
+      <c r="B47" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D47" s="9" t="s">
+      <c r="D47" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E47" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="E47" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="G47" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="11" t="s">
+      <c r="G47" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="12" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="19" t="s">
+      <c r="B48" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C48" s="20" t="s">
+      <c r="C48" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="D48" s="19" t="s">
+      <c r="D48" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F48" s="20" t="s">
+      <c r="E48" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G48" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="20" t="s">
+      <c r="G48" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="21" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="19" t="s">
+      <c r="B49" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="20" t="s">
+      <c r="C49" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="19" t="s">
+      <c r="D49" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E49" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" s="20" t="s">
+      <c r="E49" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G49" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" s="20" t="s">
+      <c r="G49" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="21" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="19" t="s">
+      <c r="B50" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E50" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="20" t="s">
+      <c r="E50" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G50" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H50" s="20" t="s">
+      <c r="G50" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="21" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C51" s="20" t="s">
+      <c r="C51" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" s="20" t="s">
+      <c r="E51" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G51" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="20" t="s">
+      <c r="G51" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="21" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="19" t="s">
+      <c r="B52" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="20" t="s">
+      <c r="C52" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="D52" s="19" t="s">
+      <c r="D52" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="20" t="s">
+      <c r="E52" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="G52" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H52" s="20" t="s">
+      <c r="G52" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="21" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="19" t="s">
+      <c r="B53" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C53" s="20" t="s">
+      <c r="C53" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="D53" s="19" t="s">
+      <c r="D53" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E53" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" s="20" t="s">
+      <c r="E53" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G53" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H53" s="20" t="s">
+      <c r="G53" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="21" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="19" t="s">
+      <c r="B54" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C54" s="20" t="s">
+      <c r="C54" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="D54" s="19" t="s">
+      <c r="D54" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" s="20" t="s">
+      <c r="E54" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="G54" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" s="20" t="s">
+      <c r="G54" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="21" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="19" t="s">
+      <c r="B55" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C55" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="D55" s="19" t="s">
+      <c r="D55" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="E55" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" s="20" t="s">
+      <c r="E55" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="G55" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="H55" s="20" t="s">
+      <c r="G55" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="21" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="9" t="s">
+      <c r="B56" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="F56" s="11" t="s">
+      <c r="E56" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="12" t="s">
         <v>159</v>
       </c>
-      <c r="G56" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" s="11" t="s">
+      <c r="G56" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="12" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="21" t="s">
+      <c r="B58" s="22" t="s">
         <v>161</v>
       </c>
-      <c r="C58" s="21"/>
-      <c r="D58" s="21"/>
-      <c r="E58" s="21"/>
-      <c r="F58" s="21"/>
-      <c r="G58" s="21"/>
-      <c r="H58" s="21"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="22"/>
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="22" t="s">
+      <c r="B59" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="D59" s="22" t="s">
+      <c r="D59" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E59" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F59" s="23" t="s">
+      <c r="E59" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="G59" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H59" s="23" t="s">
+      <c r="G59" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="24" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="22" t="s">
+      <c r="B60" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E60" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="23" t="s">
+      <c r="E60" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="G60" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H60" s="23" t="s">
+      <c r="G60" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="24" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="22" t="s">
+      <c r="B61" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="24" t="s">
         <v>170</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E61" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" s="23" t="s">
+      <c r="E61" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="24" t="s">
         <v>171</v>
       </c>
-      <c r="G61" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="23" t="s">
+      <c r="G61" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="24" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="22" t="s">
+      <c r="B62" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="24" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E62" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="23" t="s">
+      <c r="E62" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="24" t="s">
         <v>175</v>
       </c>
-      <c r="G62" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" s="23" t="s">
+      <c r="G62" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="24" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="22" t="s">
+      <c r="B63" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" s="23" t="s">
+      <c r="E63" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="G63" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H63" s="23" t="s">
+      <c r="G63" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="24" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="22" t="s">
+      <c r="B64" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E64" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" s="23" t="s">
+      <c r="E64" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="G64" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H64" s="23" t="s">
+      <c r="G64" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="24" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="22" t="s">
+      <c r="B65" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="E65" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" s="23" t="s">
+      <c r="E65" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="24" t="s">
         <v>159</v>
       </c>
-      <c r="G65" s="22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H65" s="23" t="s">
+      <c r="G65" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="24" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="24" t="s">
+      <c r="B67" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
-      <c r="F67" s="24"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="24"/>
+      <c r="C67" s="25"/>
+      <c r="D67" s="25"/>
+      <c r="E67" s="25"/>
+      <c r="F67" s="25"/>
+      <c r="G67" s="25"/>
+      <c r="H67" s="25"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B17:H17"/>
@@ -2596,6 +2627,7 @@
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B67:H67"/>
+    <mergeCell ref="A69:H69"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2615,148 +2647,148 @@
   <dimension ref="B1:E12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="B2" s="27" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="28" t="s">
         <v>187</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="D4" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="28" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="D5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="D5" s="15" t="s">
         <v>190</v>
       </c>
+      <c r="E5" s="15" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="14" t="s">
-        <v>191</v>
-      </c>
-      <c r="D6" s="14" t="s">
+      <c r="C6" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>193</v>
       </c>
+      <c r="E6" s="15" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="14" t="s">
+      <c r="C7" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>196</v>
       </c>
+      <c r="E7" s="15" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="D8" s="14" t="s">
+      <c r="C8" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>199</v>
       </c>
+      <c r="E8" s="15" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="D9" s="28" t="s">
+      <c r="C9" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="D9" s="30" t="s">
         <v>202</v>
       </c>
+      <c r="E9" s="30" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="D10" s="20" t="s">
+      <c r="C10" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>205</v>
       </c>
+      <c r="E10" s="21" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>206</v>
-      </c>
-      <c r="D11" s="20" t="s">
+      <c r="C11" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="E11" s="20" t="s">
+      <c r="D11" s="21" t="s">
         <v>208</v>
       </c>
+      <c r="E11" s="21" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="C12" s="20" t="s">
-        <v>209</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>211</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>

--- a/resources/HEARTH_Production_Timeline.xlsx
+++ b/resources/HEARTH_Production_Timeline.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="212">
   <si>
     <t xml:space="preserve">HEARTH  ·  Indie Film Production Timeline</t>
   </si>
@@ -576,9 +576,6 @@
   </si>
   <si>
     <t xml:space="preserve">⚠ = Critical milestone — do not proceed to next phase without completing this task   |   Red rows = gates that block production</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HEARTH  ·  Production Resource Library  ·  buildyourhearth.studio</t>
   </si>
   <si>
     <t xml:space="preserve">HEARTH  ·  Short Film 8-Week Quick Plan</t>
@@ -669,7 +666,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -765,14 +762,6 @@
       <b val="true"/>
       <sz val="9"/>
       <color rgb="FF8B1A0A"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF888898"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -942,15 +931,11 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1047,11 +1032,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1059,11 +1040,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1319,1307 +1300,1295 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H69"/>
+  <dimension ref="B1:H67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="1" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="3"/>
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="3" t="s">
+      <c r="E4" s="3"/>
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="5" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="4" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="9" t="s">
+      <c r="G8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H8" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="9" t="s">
+      <c r="E9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F9" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H9" s="9" t="s">
+      <c r="G9" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H9" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H10" s="9" t="s">
+      <c r="G10" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H11" s="9" t="s">
+      <c r="G11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H11" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="9" t="s">
+      <c r="G12" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H12" s="8" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H13" s="9" t="s">
+      <c r="G13" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H13" s="8" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="F14" s="9" t="s">
+      <c r="E14" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="F14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H14" s="9" t="s">
+      <c r="G14" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H14" s="8" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="12" t="s">
+      <c r="E15" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="G15" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H15" s="12" t="s">
+      <c r="G15" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="14" t="s">
+      <c r="D18" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F18" s="15" t="s">
+      <c r="E18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G18" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H18" s="15" t="s">
+      <c r="G18" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H18" s="14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="14" t="s">
+      <c r="B19" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" s="15" t="s">
+      <c r="E19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F19" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G19" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H19" s="15" t="s">
+      <c r="G19" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="14" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="15" t="s">
+      <c r="E20" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G20" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H20" s="15" t="s">
+      <c r="G20" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H20" s="14" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="14" t="s">
+      <c r="B21" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F21" s="15" t="s">
+      <c r="E21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F21" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="G21" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H21" s="15" t="s">
+      <c r="G21" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H21" s="14" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
+      <c r="B22" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="15" t="s">
+      <c r="E22" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G22" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" s="15" t="s">
+      <c r="G22" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H22" s="14" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="D23" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" s="15" t="s">
+      <c r="E23" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F23" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G23" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H23" s="15" t="s">
+      <c r="G23" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H23" s="14" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
+      <c r="B24" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="D24" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F24" s="15" t="s">
+      <c r="E24" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="G24" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H24" s="15" t="s">
+      <c r="G24" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="14" t="s">
+      <c r="B25" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D25" s="14" t="s">
+      <c r="D25" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E25" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="15" t="s">
+      <c r="E25" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H25" s="15" t="s">
+      <c r="G25" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F26" s="15" t="s">
+      <c r="E26" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F26" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H26" s="15" t="s">
+      <c r="G26" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H26" s="14" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F27" s="12" t="s">
+      <c r="E27" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F27" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H27" s="12" t="s">
+      <c r="G27" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H27" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="14" t="s">
+      <c r="B28" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="D28" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E28" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F28" s="15" t="s">
+      <c r="E28" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F28" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" s="15" t="s">
+      <c r="G28" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" s="14" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="14" t="s">
+      <c r="B29" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F29" s="15" t="s">
+      <c r="E29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="G29" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H29" s="15" t="s">
+      <c r="G29" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H29" s="14" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="D30" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F30" s="15" t="s">
+      <c r="E30" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H30" s="15" t="s">
+      <c r="G30" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H30" s="14" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="14" t="s">
+      <c r="B31" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="D31" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F31" s="15" t="s">
+      <c r="E31" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F31" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="G31" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" s="15" t="s">
+      <c r="G31" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H31" s="14" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D32" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F32" s="15" t="s">
+      <c r="E32" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="F32" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" s="15" t="s">
+      <c r="G32" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H32" s="14" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="34" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="17" t="s">
+      <c r="B35" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="17" t="s">
+      <c r="D35" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E35" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F35" s="18" t="s">
+      <c r="E35" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F35" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H35" s="18" t="s">
+      <c r="G35" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H35" s="17" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="17" t="s">
         <v>98</v>
       </c>
-      <c r="D36" s="17" t="s">
+      <c r="D36" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E36" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F36" s="18" t="s">
+      <c r="E36" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F36" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="G36" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H36" s="18" t="s">
+      <c r="G36" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H36" s="17" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="17" t="s">
+      <c r="B37" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D37" s="17" t="s">
+      <c r="D37" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E37" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F37" s="18" t="s">
+      <c r="E37" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F37" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="G37" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H37" s="18" t="s">
+      <c r="G37" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H37" s="17" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="17" t="s">
+      <c r="B38" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D38" s="17" t="s">
+      <c r="D38" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E38" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="18" t="s">
+      <c r="E38" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="G38" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H38" s="18" t="s">
+      <c r="G38" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" s="17" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F39" s="12" t="s">
+      <c r="E39" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F39" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G39" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" s="12" t="s">
+      <c r="G39" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" s="11" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="17" t="s">
+      <c r="B40" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D40" s="17" t="s">
+      <c r="D40" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E40" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F40" s="18" t="s">
+      <c r="E40" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F40" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G40" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H40" s="18" t="s">
+      <c r="G40" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H40" s="17" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="17" t="s">
+      <c r="B41" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D41" s="17" t="s">
+      <c r="D41" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="E41" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="F41" s="18" t="s">
+      <c r="E41" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="F41" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="G41" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" s="18" t="s">
+      <c r="G41" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H41" s="17" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="43" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="19" t="s">
+      <c r="B43" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="20" t="s">
         <v>118</v>
       </c>
-      <c r="D44" s="20" t="s">
+      <c r="D44" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E44" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F44" s="21" t="s">
+      <c r="E44" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="G44" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H44" s="21" t="s">
+      <c r="G44" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="20" t="s">
         <v>120</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="20" t="s">
         <v>122</v>
       </c>
-      <c r="D45" s="20" t="s">
+      <c r="D45" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F45" s="21" t="s">
+      <c r="E45" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F45" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="G45" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H45" s="21" t="s">
+      <c r="G45" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H45" s="20" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="20" t="s">
         <v>126</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E46" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F46" s="21" t="s">
+      <c r="E46" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F46" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="G46" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H46" s="21" t="s">
+      <c r="G46" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H46" s="20" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E47" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F47" s="12" t="s">
+      <c r="E47" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F47" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="G47" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H47" s="12" t="s">
+      <c r="G47" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H47" s="11" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="20" t="s">
         <v>134</v>
       </c>
-      <c r="D48" s="20" t="s">
+      <c r="D48" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E48" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F48" s="21" t="s">
+      <c r="E48" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F48" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="G48" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H48" s="21" t="s">
+      <c r="G48" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H48" s="20" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C49" s="20" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="20" t="s">
+      <c r="D49" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E49" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F49" s="21" t="s">
+      <c r="E49" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F49" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="G49" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" s="21" t="s">
+      <c r="G49" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H49" s="20" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="20" t="s">
         <v>140</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E50" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F50" s="21" t="s">
+      <c r="E50" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F50" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="G50" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H50" s="21" t="s">
+      <c r="G50" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H50" s="20" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="20" t="s">
         <v>142</v>
       </c>
-      <c r="D51" s="20" t="s">
+      <c r="D51" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E51" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F51" s="21" t="s">
+      <c r="E51" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F51" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="G51" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H51" s="21" t="s">
+      <c r="G51" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H51" s="20" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="20" t="s">
+      <c r="B52" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E52" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F52" s="21" t="s">
+      <c r="E52" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F52" s="20" t="s">
         <v>146</v>
       </c>
-      <c r="G52" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H52" s="21" t="s">
+      <c r="G52" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H52" s="20" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="D53" s="20" t="s">
+      <c r="D53" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E53" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F53" s="21" t="s">
+      <c r="E53" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F53" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="G53" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H53" s="21" t="s">
+      <c r="G53" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H53" s="20" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="20" t="s">
+      <c r="B54" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C54" s="21" t="s">
+      <c r="C54" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="D54" s="20" t="s">
+      <c r="D54" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E54" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F54" s="21" t="s">
+      <c r="E54" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F54" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="G54" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H54" s="21" t="s">
+      <c r="G54" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H54" s="20" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="20" t="s">
+      <c r="B55" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C55" s="21" t="s">
+      <c r="C55" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="D55" s="20" t="s">
+      <c r="D55" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="E55" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="F55" s="21" t="s">
+      <c r="E55" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F55" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="G55" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="H55" s="21" t="s">
+      <c r="G55" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H55" s="20" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="C56" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F56" s="12" t="s">
+      <c r="E56" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="F56" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G56" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H56" s="12" t="s">
+      <c r="G56" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H56" s="11" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="58" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="22" t="s">
+      <c r="B58" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="22"/>
-      <c r="H58" s="22"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
+      <c r="F58" s="21"/>
+      <c r="G58" s="21"/>
+      <c r="H58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="23" t="s">
+      <c r="B59" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="D59" s="23" t="s">
+      <c r="D59" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E59" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F59" s="24" t="s">
+      <c r="E59" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F59" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G59" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H59" s="24" t="s">
+      <c r="G59" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H59" s="23" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="22" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="C60" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="D60" s="23" t="s">
+      <c r="D60" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E60" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F60" s="24" t="s">
+      <c r="E60" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F60" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="G60" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H60" s="24" t="s">
+      <c r="G60" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H60" s="23" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="23" t="s">
+      <c r="B61" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="D61" s="23" t="s">
+      <c r="D61" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E61" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F61" s="24" t="s">
+      <c r="E61" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F61" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="G61" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H61" s="24" t="s">
+      <c r="G61" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H61" s="23" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B62" s="23" t="s">
+      <c r="B62" s="22" t="s">
         <v>173</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="D62" s="23" t="s">
+      <c r="D62" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E62" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="24" t="s">
+      <c r="E62" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="G62" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" s="24" t="s">
+      <c r="G62" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H62" s="23" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B63" s="23" t="s">
+      <c r="B63" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E63" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F63" s="24" t="s">
+      <c r="E63" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F63" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G63" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H63" s="24" t="s">
+      <c r="G63" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H63" s="23" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B64" s="23" t="s">
+      <c r="B64" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="C64" s="24" t="s">
+      <c r="C64" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="D64" s="23" t="s">
+      <c r="D64" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E64" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F64" s="24" t="s">
+      <c r="E64" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F64" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G64" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H64" s="24" t="s">
+      <c r="G64" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H64" s="23" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B65" s="23" t="s">
+      <c r="B65" s="22" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="D65" s="23" t="s">
+      <c r="D65" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="E65" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F65" s="24" t="s">
+      <c r="E65" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="F65" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="G65" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="H65" s="24" t="s">
+      <c r="G65" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="H65" s="23" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="67" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B67" s="25" t="s">
+      <c r="B67" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="C67" s="25"/>
-      <c r="D67" s="25"/>
-      <c r="E67" s="25"/>
-      <c r="F67" s="25"/>
-      <c r="G67" s="25"/>
-      <c r="H67" s="25"/>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="26" t="s">
-        <v>185</v>
-      </c>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
-      <c r="D69" s="26"/>
-      <c r="E69" s="26"/>
-      <c r="F69" s="26"/>
-      <c r="G69" s="26"/>
-      <c r="H69" s="26"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="24"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="24"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B7:H7"/>
     <mergeCell ref="B17:H17"/>
@@ -2627,7 +2596,6 @@
     <mergeCell ref="B43:H43"/>
     <mergeCell ref="B58:H58"/>
     <mergeCell ref="B67:H67"/>
-    <mergeCell ref="A69:H69"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2647,148 +2615,148 @@
   <dimension ref="B1:E12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="2" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="B2" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
     </row>
     <row r="3" customFormat="false" ht="7.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="E4" s="26" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E5" s="15" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="14" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="E6" s="15" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="E7" s="15" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="E8" s="15" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="28" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="29" t="s">
-        <v>46</v>
-      </c>
-      <c r="C9" s="30" t="s">
+      <c r="D9" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="E9" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E9" s="30" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" s="21" t="s">
+      <c r="D10" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="20" t="s">
         <v>205</v>
       </c>
-      <c r="E10" s="21" t="s">
+    </row>
+    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="C11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="E11" s="20" t="s">
         <v>208</v>
       </c>
-      <c r="E11" s="21" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="21" t="s">
+      <c r="D12" s="20" t="s">
         <v>210</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="E12" s="20" t="s">
         <v>211</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>212</v>
       </c>
     </row>
   </sheetData>
